--- a/MILP/model_output/connections_generated.xlsx
+++ b/MILP/model_output/connections_generated.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="18">
   <si>
     <t>Node (i)</t>
   </si>
@@ -43,16 +43,31 @@
     <t>Aarau</t>
   </si>
   <si>
-    <t>Baselwolf</t>
-  </si>
-  <si>
-    <t>Chiasso</t>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Bern</t>
+  </si>
+  <si>
+    <t>Lausanne</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Olten</t>
+  </si>
+  <si>
+    <t>Schaffhausen</t>
   </si>
   <si>
     <t>Stabio</t>
   </si>
   <si>
     <t>Visp</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
   </si>
 </sst>
 </file>
@@ -410,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -453,10 +468,10 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>155.63758</v>
+        <v>81</v>
       </c>
       <c r="G2">
         <v>80</v>
@@ -479,10 +494,10 @@
         <v>11</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>155.63758</v>
+        <v>173</v>
       </c>
       <c r="G3">
         <v>80</v>
@@ -496,19 +511,19 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>151.515715</v>
+        <v>95</v>
       </c>
       <c r="G4">
         <v>80</v>
@@ -519,22 +534,22 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>157.7173901587302</v>
+        <v>221</v>
       </c>
       <c r="G5">
         <v>80</v>
@@ -545,22 +560,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>155.47652625</v>
+        <v>161</v>
       </c>
       <c r="G6">
         <v>80</v>
@@ -571,22 +586,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>157.6675138592233</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>80</v>
@@ -597,22 +612,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>155.47652625</v>
+        <v>271</v>
       </c>
       <c r="G8">
         <v>80</v>
@@ -623,27 +638,521 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>93</v>
+      </c>
+      <c r="G9">
+        <v>80</v>
+      </c>
+      <c r="H9">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>173</v>
+      </c>
+      <c r="G10">
+        <v>80</v>
+      </c>
+      <c r="H10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
         <v>5</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>193</v>
+      </c>
+      <c r="G11">
+        <v>80</v>
+      </c>
+      <c r="H11">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>185</v>
+      </c>
+      <c r="G12">
+        <v>80</v>
+      </c>
+      <c r="H12">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>235</v>
+      </c>
+      <c r="G13">
+        <v>80</v>
+      </c>
+      <c r="H13">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>95</v>
+      </c>
+      <c r="G14">
+        <v>80</v>
+      </c>
+      <c r="H14">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>136</v>
+      </c>
+      <c r="G15">
+        <v>80</v>
+      </c>
+      <c r="H15">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>221</v>
+      </c>
+      <c r="G16">
+        <v>80</v>
+      </c>
+      <c r="H16">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17">
         <v>3</v>
       </c>
-      <c r="F9">
-        <v>152.065055</v>
-      </c>
-      <c r="G9">
-        <v>80</v>
-      </c>
-      <c r="H9">
+      <c r="F17">
+        <v>271</v>
+      </c>
+      <c r="G17">
+        <v>80</v>
+      </c>
+      <c r="H17">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
+        <v>8</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>235</v>
+      </c>
+      <c r="G18">
+        <v>80</v>
+      </c>
+      <c r="H18">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
+        <v>8</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>257</v>
+      </c>
+      <c r="G19">
+        <v>80</v>
+      </c>
+      <c r="H19">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
+        <v>8</v>
+      </c>
+      <c r="B20">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>227</v>
+      </c>
+      <c r="G20">
+        <v>80</v>
+      </c>
+      <c r="H20">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21">
+        <v>9</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>161</v>
+      </c>
+      <c r="G21">
+        <v>80</v>
+      </c>
+      <c r="H21">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
+        <v>9</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>187</v>
+      </c>
+      <c r="G22">
+        <v>80</v>
+      </c>
+      <c r="H22">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23">
+        <v>9</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>93</v>
+      </c>
+      <c r="G23">
+        <v>80</v>
+      </c>
+      <c r="H23">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24">
+        <v>9</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>153</v>
+      </c>
+      <c r="G24">
+        <v>80</v>
+      </c>
+      <c r="H24">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25">
+        <v>9</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>334</v>
+      </c>
+      <c r="G25">
+        <v>80</v>
+      </c>
+      <c r="H25">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26">
+        <v>10</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>65</v>
+      </c>
+      <c r="G26">
+        <v>80</v>
+      </c>
+      <c r="H26">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27">
+        <v>10</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>106</v>
+      </c>
+      <c r="G27">
+        <v>80</v>
+      </c>
+      <c r="H27">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>10</v>
+      </c>
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>227</v>
+      </c>
+      <c r="G28">
+        <v>80</v>
+      </c>
+      <c r="H28">
         <v>4000</v>
       </c>
     </row>
